--- a/data/Availability Calendar.xlsx
+++ b/data/Availability Calendar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aalshareef\Downloads\History\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elhamid\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F18DE23-4685-4296-939B-924418102021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F931BD4-3D52-44C5-8FDF-2173F789D689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="26" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47355,7 +47355,7 @@
       <c r="P5" s="46"/>
       <c r="Q5" s="23"/>
       <c r="R5" s="23"/>
-      <c r="S5" s="46"/>
+      <c r="S5" s="23"/>
       <c r="T5" s="46"/>
       <c r="U5" s="46"/>
       <c r="V5" s="46"/>
@@ -47391,7 +47391,7 @@
       <c r="P6" s="23"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23"/>
-      <c r="S6" s="46"/>
+      <c r="S6" s="23"/>
       <c r="T6" s="46"/>
       <c r="U6" s="46"/>
       <c r="V6" s="46"/>
@@ -48039,7 +48039,7 @@
       <c r="P19" s="23"/>
       <c r="Q19" s="23"/>
       <c r="R19" s="23"/>
-      <c r="S19" s="46"/>
+      <c r="S19" s="23"/>
       <c r="T19" s="46"/>
       <c r="U19" s="46"/>
       <c r="V19" s="46"/>
@@ -48689,7 +48689,7 @@
       <c r="R32" s="23"/>
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
+      <c r="U32" s="46"/>
       <c r="V32" s="46"/>
       <c r="W32" s="46"/>
       <c r="X32" s="46"/>
@@ -48761,7 +48761,7 @@
       <c r="R34" s="23"/>
       <c r="S34" s="23"/>
       <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
+      <c r="U34" s="46"/>
       <c r="V34" s="46"/>
       <c r="W34" s="46"/>
       <c r="X34" s="46"/>
@@ -49191,7 +49191,7 @@
       <c r="P41" s="46"/>
       <c r="Q41" s="23"/>
       <c r="R41" s="23"/>
-      <c r="S41" s="46"/>
+      <c r="S41" s="23"/>
       <c r="T41" s="46"/>
       <c r="U41" s="46"/>
       <c r="V41" s="46"/>
@@ -49227,7 +49227,7 @@
       <c r="P42" s="46"/>
       <c r="Q42" s="23"/>
       <c r="R42" s="23"/>
-      <c r="S42" s="46"/>
+      <c r="S42" s="23"/>
       <c r="T42" s="46"/>
       <c r="U42" s="46"/>
       <c r="V42" s="46"/>
@@ -49263,7 +49263,7 @@
       <c r="P43" s="46"/>
       <c r="Q43" s="23"/>
       <c r="R43" s="23"/>
-      <c r="S43" s="46"/>
+      <c r="S43" s="23"/>
       <c r="T43" s="46"/>
       <c r="U43" s="46"/>
       <c r="V43" s="46"/>
@@ -49299,7 +49299,7 @@
       <c r="P44" s="46"/>
       <c r="Q44" s="23"/>
       <c r="R44" s="23"/>
-      <c r="S44" s="46"/>
+      <c r="S44" s="23"/>
       <c r="T44" s="46"/>
       <c r="U44" s="46"/>
       <c r="V44" s="46"/>
@@ -49335,7 +49335,7 @@
       <c r="P45" s="46"/>
       <c r="Q45" s="46"/>
       <c r="R45" s="23"/>
-      <c r="S45" s="46"/>
+      <c r="S45" s="23"/>
       <c r="T45" s="46"/>
       <c r="U45" s="46"/>
       <c r="V45" s="46"/>
@@ -49371,7 +49371,7 @@
       <c r="P46" s="46"/>
       <c r="Q46" s="46"/>
       <c r="R46" s="23"/>
-      <c r="S46" s="46"/>
+      <c r="S46" s="23"/>
       <c r="T46" s="46"/>
       <c r="U46" s="46"/>
       <c r="V46" s="46"/>
